--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486927_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486927_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.5358</v>
+        <v>11.599</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1553</v>
+        <v>7.7442</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3805</v>
+        <v>3.8548</v>
       </c>
       <c r="G2" t="n">
         <v>8.1236</v>
@@ -610,13 +610,13 @@
         <v>2.8748</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7028</v>
+        <v>0.3604</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5928</v>
+        <v>-0.004</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.11</v>
+        <v>0.3643</v>
       </c>
       <c r="V2" t="n">
         <v>0.2402</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. FRITZ</t>
+          <t>H. FIGUEROA ÁLVAREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6165</v>
+        <v>6.7136</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2637</v>
+        <v>5.0946</v>
       </c>
       <c r="F3" t="n">
-        <v>6.8802</v>
+        <v>1.619</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8504</v>
+        <v>5.6075</v>
       </c>
       <c r="H3" t="n">
-        <v>1.077</v>
+        <v>1.064</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7733</v>
+        <v>4.5436</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6236</v>
+        <v>6.8223</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2687</v>
+        <v>1.5607</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3549</v>
+        <v>5.2616</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2268</v>
+        <v>-1.2147</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1917</v>
+        <v>-0.4967</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4185</v>
+        <v>-0.7181</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4107</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R3" t="n">
-        <v>2.6694</v>
+        <v>1.8481</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4561</v>
+        <v>0.4601</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1704</v>
+        <v>-0.5038</v>
       </c>
       <c r="U3" t="n">
-        <v>2.2858</v>
+        <v>0.9639</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7207</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0225</v>
+        <v>0.8295</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6982</v>
+        <v>0.0218</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>J. FRITZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.9626</v>
+        <v>5.9553</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6103</v>
+        <v>-0.3024</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3522</v>
+        <v>6.2577</v>
       </c>
       <c r="G4" t="n">
-        <v>5.6075</v>
+        <v>3.8504</v>
       </c>
       <c r="H4" t="n">
-        <v>1.064</v>
+        <v>1.077</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5436</v>
+        <v>2.7733</v>
       </c>
       <c r="J4" t="n">
-        <v>6.8223</v>
+        <v>2.6236</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5607</v>
+        <v>1.2687</v>
       </c>
       <c r="L4" t="n">
-        <v>5.2616</v>
+        <v>1.3549</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2147</v>
+        <v>1.2268</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4967</v>
+        <v>-0.1917</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7181</v>
+        <v>1.4185</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2053</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8481</v>
+        <v>2.6694</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.291</v>
+        <v>1.7949</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9881</v>
+        <v>0.1316</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6971000000000001</v>
+        <v>1.6633</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.7207</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8295</v>
+        <v>0.0225</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0218</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. CARREIRA KREPS</t>
+          <t>G. RODRIGUEZ SOLER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5682</v>
+        <v>3.0357</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3168</v>
+        <v>2.0125</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2514</v>
+        <v>1.0232</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0871</v>
+        <v>3.241</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7951</v>
+        <v>0.8467</v>
       </c>
       <c r="I5" t="n">
-        <v>1.292</v>
+        <v>2.3944</v>
       </c>
       <c r="J5" t="n">
-        <v>0.871</v>
+        <v>4.1745</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6287</v>
+        <v>0.8988</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4997</v>
+        <v>3.2757</v>
       </c>
       <c r="M5" t="n">
-        <v>1.2161</v>
+        <v>-0.9335</v>
       </c>
       <c r="N5" t="n">
-        <v>1.4238</v>
+        <v>-0.0522</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2077</v>
+        <v>-0.8813</v>
       </c>
       <c r="P5" t="n">
-        <v>0.616</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R5" t="n">
-        <v>2.6694</v>
+        <v>2.0534</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0437</v>
+        <v>-0.2053</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4992</v>
+        <v>-0.1086</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5445</v>
+        <v>-0.0968</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4176</v>
+        <v>2.9326</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4115</v>
+        <v>3.1636</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0061</v>
+        <v>-0.231</v>
       </c>
       <c r="G6" t="n">
         <v>2.0944</v>
@@ -922,13 +922,13 @@
         <v>1.0267</v>
       </c>
       <c r="S6" t="n">
-        <v>1.322</v>
+        <v>0.8369</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3021</v>
+        <v>0.0542</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0199</v>
+        <v>0.7827</v>
       </c>
       <c r="V6" t="n">
         <v>-1.0255</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. BADMUS</t>
+          <t>M. CARREIRA KREPS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.3908</v>
+        <v>2.7362</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5989</v>
+        <v>-0.6634</v>
       </c>
       <c r="F7" t="n">
-        <v>0.792</v>
+        <v>3.3996</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4618</v>
+        <v>2.0871</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6781</v>
+        <v>0.7951</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7837</v>
+        <v>1.292</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9163</v>
+        <v>0.871</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7855</v>
+        <v>-0.6287</v>
       </c>
       <c r="L7" t="n">
-        <v>3.1308</v>
+        <v>1.4997</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4545</v>
+        <v>1.2161</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1074</v>
+        <v>1.4238</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3472</v>
+        <v>-0.2077</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8481</v>
+        <v>2.6694</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7237</v>
+        <v>1.2117</v>
       </c>
       <c r="T7" t="n">
-        <v>0.736</v>
+        <v>0.5191</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0123</v>
+        <v>0.6927</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5893</v>
+        <v>-1.1786</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5893</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ SOLER</t>
+          <t>A. BADMUS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3143</v>
+        <v>2.7039</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5282</v>
+        <v>1.9712</v>
       </c>
       <c r="F8" t="n">
-        <v>0.786</v>
+        <v>0.7327</v>
       </c>
       <c r="G8" t="n">
-        <v>3.241</v>
+        <v>3.4618</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8467</v>
+        <v>0.6781</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3944</v>
+        <v>2.7837</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1745</v>
+        <v>3.9163</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8988</v>
+        <v>0.7855</v>
       </c>
       <c r="L8" t="n">
-        <v>3.2757</v>
+        <v>3.1308</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9335</v>
+        <v>-0.4545</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0522</v>
+        <v>-0.1074</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8813</v>
+        <v>-0.3472</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0534</v>
+        <v>1.8481</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9268</v>
+        <v>0.0368</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5928</v>
+        <v>0.1084</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3339</v>
+        <v>-0.0716</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="9">
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.2272</v>
+        <v>2.4364</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3993</v>
+        <v>-1.1901</v>
       </c>
       <c r="F9" t="n">
         <v>3.6265</v>
@@ -1156,10 +1156,10 @@
         <v>1.6427</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2558</v>
+        <v>0.465</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5928</v>
+        <v>-0.3836</v>
       </c>
       <c r="U9" t="n">
         <v>0.8486</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.1134</v>
+        <v>1.9159</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7036</v>
+        <v>-1.2193</v>
       </c>
       <c r="F10" t="n">
-        <v>3.8171</v>
+        <v>3.1353</v>
       </c>
       <c r="G10" t="n">
         <v>1.9067</v>
@@ -1234,13 +1234,13 @@
         <v>2.0534</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9715</v>
+        <v>0.774</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8563</v>
+        <v>-0.3721</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8278</v>
+        <v>1.146</v>
       </c>
       <c r="V10" t="n">
         <v>0.262</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4619</v>
+        <v>1.078</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4285</v>
+        <v>-0.9902</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8904</v>
+        <v>2.0682</v>
       </c>
       <c r="G11" t="n">
         <v>0.2238</v>
@@ -1312,13 +1312,13 @@
         <v>1.6427</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1026</v>
+        <v>0.7187</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5384</v>
+        <v>-0.0234</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5642</v>
+        <v>0.7421</v>
       </c>
       <c r="V11" t="n">
         <v>-0.4805</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4017</v>
+        <v>0.9</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2911</v>
+        <v>0.0885</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6929</v>
+        <v>0.8114</v>
       </c>
       <c r="G12" t="n">
         <v>0.2568</v>
@@ -1390,13 +1390,13 @@
         <v>1.0267</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1449</v>
+        <v>0.6432</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3294</v>
+        <v>0.0503</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4743</v>
+        <v>0.5928</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.0384</v>
+        <v>-1.3762</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.278</v>
+        <v>-5.7937</v>
       </c>
       <c r="F13" t="n">
-        <v>4.2396</v>
+        <v>4.4175</v>
       </c>
       <c r="G13" t="n">
         <v>0.0568</v>
@@ -1468,13 +1468,13 @@
         <v>2.2588</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0286</v>
+        <v>0.6335</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9222</v>
+        <v>-0.4379</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8935999999999999</v>
+        <v>1.0714</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2185</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>39.9716</v>
+        <v>40.63040000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>9.256799999999998</v>
+        <v>9.915500000000002</v>
       </c>
       <c r="F14" t="n">
         <v>30.7149</v>
@@ -1537,7 +1537,7 @@
         <v>3.5019</v>
       </c>
       <c r="P14" t="n">
-        <v>2.0534</v>
+        <v>2.053400000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-21.5607</v>
@@ -1546,13 +1546,13 @@
         <v>23.6142</v>
       </c>
       <c r="S14" t="n">
-        <v>7.0711</v>
+        <v>7.7299</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.6283</v>
+        <v>-0.9698</v>
       </c>
       <c r="U14" t="n">
-        <v>8.6996</v>
+        <v>8.699400000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-1.3964</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.1899</v>
+        <v>-1.4881</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4205</v>
+        <v>0.2113</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6105</v>
+        <v>-1.6994</v>
       </c>
       <c r="G15" t="n">
         <v>-5.0578</v>
@@ -1624,13 +1624,13 @@
         <v>2.8748</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6599</v>
+        <v>-0.958</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0812</v>
+        <v>-1.2904</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4213</v>
+        <v>0.3324</v>
       </c>
       <c r="V15" t="n">
         <v>3.2957</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.2049</v>
+        <v>-1.5484</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.148</v>
+        <v>-1.4619</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0569</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>-1.5492</v>
@@ -1702,13 +1702,13 @@
         <v>2.6694</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4073</v>
+        <v>-0.7507</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8836000000000001</v>
+        <v>-1.1974</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4763</v>
+        <v>0.4467</v>
       </c>
       <c r="V16" t="n">
         <v>-0.4805</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. VALERA COROMINAS</t>
+          <t>P. SALA VALLMAJO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.1417</v>
+        <v>-2.2412</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7534</v>
+        <v>-1.2982</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3882</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.2276</v>
+        <v>-0.8077</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4965</v>
+        <v>0.9893</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7311</v>
+        <v>-1.797</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5600000000000001</v>
+        <v>1.2783</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.639</v>
+        <v>1.2653</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0789</v>
+        <v>0.013</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6676</v>
+        <v>-2.086</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1425</v>
+        <v>-0.2759</v>
       </c>
       <c r="O17" t="n">
         <v>-1.8101</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4107</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.2321</v>
+        <v>-2.2588</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.4068</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0386</v>
+        <v>-0.3178</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1231</v>
+        <v>-0.0891</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. SALA VALLMAJO</t>
+          <t>I. VALERA COROMINAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.569</v>
+        <v>-2.2916</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5074</v>
+        <v>-1.9626</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0616</v>
+        <v>-0.3289</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8077</v>
+        <v>-2.2276</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9893</v>
+        <v>-0.4965</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.797</v>
+        <v>-1.7311</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2783</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2653</v>
+        <v>-0.639</v>
       </c>
       <c r="L18" t="n">
-        <v>0.013</v>
+        <v>0.0789</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.086</v>
+        <v>-1.6676</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2759</v>
+        <v>0.1425</v>
       </c>
       <c r="O18" t="n">
         <v>-1.8101</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.0267</v>
+        <v>0.4107</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2588</v>
+        <v>-1.2321</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2321</v>
+        <v>1.6427</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7346</v>
+        <v>-0.2344</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.527</v>
+        <v>-0.1706</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2076</v>
+        <v>-0.0638</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.2554</v>
+        <v>-3.421</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2482</v>
+        <v>-2.562</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0073</v>
+        <v>-0.859</v>
       </c>
       <c r="G19" t="n">
         <v>-0.293</v>
@@ -1936,13 +1936,13 @@
         <v>1.8481</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3546</v>
+        <v>-0.5202</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3566</v>
+        <v>-0.6704</v>
       </c>
       <c r="U19" t="n">
-        <v>0.002</v>
+        <v>0.1502</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3491</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7436</v>
+        <v>-4.7235</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2542</v>
+        <v>-2.4634</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4894</v>
+        <v>-2.2601</v>
       </c>
       <c r="G20" t="n">
         <v>-4.0281</v>
@@ -2014,13 +2014,13 @@
         <v>2.8748</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3194</v>
+        <v>-0.6606</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8177</v>
+        <v>-1.0269</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1371</v>
+        <v>0.3664</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2402</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.1884</v>
+        <v>-4.7264</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.4405</v>
+        <v>-4.1267</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7479</v>
+        <v>-0.5997</v>
       </c>
       <c r="G21" t="n">
         <v>-5.3104</v>
@@ -2092,13 +2092,13 @@
         <v>1.6427</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3154</v>
+        <v>-0.8534</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8563</v>
+        <v>-0.5425</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4591</v>
+        <v>-0.3109</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2989</v>
+        <v>-5.0897</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.1627</v>
+        <v>-5.9535</v>
       </c>
       <c r="F22" t="n">
         <v>0.8638</v>
@@ -2170,10 +2170,10 @@
         <v>1.6427</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8058999999999999</v>
+        <v>-0.5967</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1857</v>
+        <v>-0.9765</v>
       </c>
       <c r="U22" t="n">
         <v>0.3798</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.4328</v>
+        <v>-5.2236</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.0842</v>
+        <v>-4.875</v>
       </c>
       <c r="F23" t="n">
         <v>-0.3486</v>
@@ -2248,10 +2248,10 @@
         <v>2.6694</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2243</v>
+        <v>-1.0151</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.5809</v>
+        <v>-1.3717</v>
       </c>
       <c r="U23" t="n">
         <v>0.3566</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.946899999999999</v>
+        <v>-9.2181</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.5365</v>
+        <v>-6.2227</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.4104</v>
+        <v>-2.9954</v>
       </c>
       <c r="G24" t="n">
         <v>-6.1778</v>
@@ -2326,13 +2326,13 @@
         <v>2.4641</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.804</v>
+        <v>-1.0752</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.4492</v>
+        <v>-1.1354</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3548</v>
+        <v>0.0602</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9384</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-39.9715</v>
+        <v>-39.9716</v>
       </c>
       <c r="E25" t="n">
-        <v>-30.7146</v>
+        <v>-30.7147</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.257000000000001</v>
+        <v>-9.256800000000002</v>
       </c>
       <c r="G25" t="n">
         <v>-32.24339999999999</v>
@@ -2404,10 +2404,10 @@
         <v>21.5608</v>
       </c>
       <c r="S25" t="n">
-        <v>-7.071099999999999</v>
+        <v>-7.0711</v>
       </c>
       <c r="T25" t="n">
-        <v>-8.699599999999998</v>
+        <v>-8.6996</v>
       </c>
       <c r="U25" t="n">
         <v>1.6285</v>
